--- a/cortes-madecentro-fondo-RH6-blanco-medidas-finales.xlsx
+++ b/cortes-madecentro-fondo-RH6-blanco-medidas-finales.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cortes" sheetId="1" r:id="Rbd385416b8474e2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R4760f08cb13a4340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control del pedido" sheetId="3" r:id="R8355e83e53e344c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recepción y canteo" sheetId="4" r:id="Ra08ae71167964a24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cortes" sheetId="1" r:id="R7473679bfd3f4b4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" r:id="R6210ea2a283743de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control del pedido" sheetId="3" r:id="Ree589a79c803496b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Recepción y canteo" sheetId="4" r:id="R920c20e011a24a27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1601,7 +1601,7 @@
         <x:v>Origen</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>Pedido único del proyecto. Revisión local del 27/10/2026: un solo tipo de canto por pieza, contrastado con los tres despieces y manifiestos 3D.</x:v>
+        <x:v>Pedido único del proyecto, revisión del 28/10/2026: clóset sin panel trasero, con marco completo C3-025 a C3-030. Sustituye las piezas C3-005 y C3-011 del PDF anterior. Un solo tipo de canto por pieza; contrastado con los tres despieces y manifiestos 3D.</x:v>
       </x:c>
       <x:c r="C5" s="8"/>
       <x:c r="D5" s="8"/>
